--- a/diseases/d155/2005-2009.xlsx
+++ b/diseases/d155/2005-2009.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -33994,7 +33994,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -34948,7 +34948,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36856,7 +36856,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37810,7 +37810,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38764,7 +38764,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39718,7 +39718,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40672,7 +40672,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41626,7 +41626,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43534,7 +43534,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -52040,7 +52040,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -54805,7 +54805,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -56713,7 +56713,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -57667,7 +57667,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -58621,7 +58621,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -59575,7 +59575,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -60529,7 +60529,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -61483,7 +61483,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -62437,7 +62437,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -63391,7 +63391,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -64345,7 +64345,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -72851,7 +72851,7 @@
       </c>
       <c r="AM374" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN374" t="b">
@@ -75616,7 +75616,7 @@
       </c>
       <c r="AM388" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN388" t="b">
@@ -76570,7 +76570,7 @@
       </c>
       <c r="AM393" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN393" t="b">
@@ -77524,7 +77524,7 @@
       </c>
       <c r="AM398" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN398" t="b">
@@ -78478,7 +78478,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN403" t="b">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -80386,7 +80386,7 @@
       </c>
       <c r="AM413" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN413" t="b">
@@ -81340,7 +81340,7 @@
       </c>
       <c r="AM418" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN418" t="b">
@@ -82294,7 +82294,7 @@
       </c>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN423" t="b">
@@ -83248,7 +83248,7 @@
       </c>
       <c r="AM428" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN428" t="b">
@@ -84202,7 +84202,7 @@
       </c>
       <c r="AM433" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN433" t="b">
@@ -85156,7 +85156,7 @@
       </c>
       <c r="AM438" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN438" t="b">
